--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:20:05+00:00</t>
+    <t>2026-07-28T10:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:50:36+00:00</t>
+    <t>2026-07-29T08:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG references but does not redistribute SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); value sets enumerate concept identifiers only, so display terms are supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -796,6 +799,10 @@
   <si>
     <t xml:space="preserve">nor-1
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+iddsi-axis-fluid:A food-axis IDDSI concept must not be used on fluidConsistencyType, which carries the drink axis (IDDSI Levels 0-4). {fluidConsistencyType.coding.where(system = 'http://snomed.info/sct' and code in ('1237447009' | '1237448004' | '1237449007' | '1237450007' | '1237451006')).empty()}iddsi-axis-food:A drink-only IDDSI concept must not be used on texture.modifier, which carries the food axis. IDDSI Level 3 (1237444002) is a single concept shared by both axes and is therefore permitted here. {texture.modifier.coding.where(system = 'http://snomed.info/sct' and code in ('1231508001' | '1237441005' | '1237442003' | '1237446000')).empty()}</t>
   </si>
   <si>
     <t>ODS-1 Value = "D"</t>
@@ -1598,54 +1605,56 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1701,143 +1710,143 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>18</v>
@@ -1849,16 +1858,16 @@
         <v>18</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1908,28 +1917,28 @@
         <v>18</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>18</v>
@@ -1937,10 +1946,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1948,10 +1957,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>18</v>
@@ -1960,19 +1969,19 @@
         <v>18</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2022,13 +2031,13 @@
         <v>18</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>18</v>
@@ -2051,10 +2060,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2062,10 +2071,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>18</v>
@@ -2074,16 +2083,16 @@
         <v>18</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2134,19 +2143,19 @@
         <v>18</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>18</v>
@@ -2163,10 +2172,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2174,31 +2183,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2248,19 +2257,19 @@
         <v>18</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>18</v>
@@ -2277,10 +2286,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2288,10 +2297,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>18</v>
@@ -2303,16 +2312,16 @@
         <v>18</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2338,13 +2347,13 @@
         <v>18</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>18</v>
@@ -2362,19 +2371,19 @@
         <v>18</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>18</v>
@@ -2391,21 +2400,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>18</v>
@@ -2417,16 +2426,16 @@
         <v>18</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2476,19 +2485,19 @@
         <v>18</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>18</v>
@@ -2497,7 +2506,7 @@
         <v>18</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>18</v>
@@ -2505,21 +2514,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>18</v>
@@ -2531,16 +2540,16 @@
         <v>18</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2590,13 +2599,13 @@
         <v>18</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>18</v>
@@ -2611,7 +2620,7 @@
         <v>18</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>18</v>
@@ -2619,21 +2628,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>18</v>
@@ -2645,16 +2654,16 @@
         <v>18</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2704,19 +2713,19 @@
         <v>18</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>18</v>
@@ -2725,7 +2734,7 @@
         <v>18</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>18</v>
@@ -2733,45 +2742,45 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>18</v>
@@ -2820,19 +2829,19 @@
         <v>18</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>18</v>
@@ -2841,7 +2850,7 @@
         <v>18</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>18</v>
@@ -2849,10 +2858,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2860,10 +2869,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>18</v>
@@ -2875,16 +2884,16 @@
         <v>18</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2934,39 +2943,39 @@
         <v>18</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2974,10 +2983,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
@@ -2986,19 +2995,19 @@
         <v>18</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3048,28 +3057,28 @@
         <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>18</v>
@@ -3077,10 +3086,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3088,10 +3097,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>18</v>
@@ -3100,19 +3109,19 @@
         <v>18</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3162,28 +3171,28 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>18</v>
@@ -3191,10 +3200,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3202,10 +3211,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>18</v>
@@ -3217,13 +3226,13 @@
         <v>18</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3274,28 +3283,28 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>18</v>
@@ -3303,10 +3312,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3314,31 +3323,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3364,13 +3373,13 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -3388,74 +3397,74 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>18</v>
@@ -3480,13 +3489,13 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -3504,39 +3513,39 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3544,28 +3553,28 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3616,39 +3625,39 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3656,10 +3665,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>18</v>
@@ -3671,13 +3680,13 @@
         <v>18</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3728,39 +3737,39 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3768,10 +3777,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -3780,16 +3789,16 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3840,39 +3849,39 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3880,10 +3889,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -3892,16 +3901,16 @@
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3952,39 +3961,39 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3992,10 +4001,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -4007,16 +4016,16 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4066,19 +4075,19 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>18</v>
@@ -4087,7 +4096,7 @@
         <v>18</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>18</v>
@@ -4095,10 +4104,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4106,10 +4115,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -4121,16 +4130,16 @@
         <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4156,13 +4165,13 @@
         <v>18</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>18</v>
@@ -4180,28 +4189,28 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>18</v>
@@ -4209,10 +4218,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4220,10 +4229,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>18</v>
@@ -4235,16 +4244,16 @@
         <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4270,13 +4279,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -4294,19 +4303,19 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>18</v>
@@ -4315,7 +4324,7 @@
         <v>18</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>18</v>
@@ -4323,10 +4332,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4334,10 +4343,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>18</v>
@@ -4349,13 +4358,13 @@
         <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4406,28 +4415,28 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>18</v>
@@ -4435,10 +4444,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4446,10 +4455,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>18</v>
@@ -4461,13 +4470,13 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4518,13 +4527,13 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>18</v>
@@ -4539,7 +4548,7 @@
         <v>18</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>18</v>
@@ -4547,21 +4556,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4573,16 +4582,16 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4632,19 +4641,19 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>18</v>
@@ -4653,7 +4662,7 @@
         <v>18</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>18</v>
@@ -4661,45 +4670,45 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -4748,19 +4757,19 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>18</v>
@@ -4769,7 +4778,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>18</v>
@@ -4777,10 +4786,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4788,10 +4797,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -4800,16 +4809,16 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4836,13 +4845,13 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
@@ -4860,50 +4869,50 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>18</v>
@@ -4915,13 +4924,13 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4972,28 +4981,28 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>18</v>
@@ -5001,10 +5010,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5012,10 +5021,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5027,13 +5036,13 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5084,28 +5093,28 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>18</v>
@@ -5113,10 +5122,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5124,10 +5133,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>18</v>
@@ -5139,13 +5148,13 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5196,13 +5205,13 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>18</v>
@@ -5217,7 +5226,7 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>18</v>
@@ -5225,21 +5234,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -5251,16 +5260,16 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5310,19 +5319,19 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>18</v>
@@ -5331,7 +5340,7 @@
         <v>18</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>18</v>
@@ -5339,45 +5348,45 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -5426,19 +5435,19 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
@@ -5447,7 +5456,7 @@
         <v>18</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>18</v>
@@ -5455,10 +5464,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5466,10 +5475,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
@@ -5481,13 +5490,13 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5514,13 +5523,13 @@
         <v>18</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>18</v>
@@ -5538,39 +5547,39 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5578,10 +5587,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
@@ -5593,13 +5602,13 @@
         <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5650,28 +5659,28 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>18</v>
@@ -5679,10 +5688,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5690,10 +5699,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -5705,13 +5714,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5762,28 +5771,28 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>18</v>
@@ -5791,10 +5800,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5802,10 +5811,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
@@ -5817,13 +5826,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5874,13 +5883,13 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>18</v>
@@ -5895,7 +5904,7 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>18</v>
@@ -5903,21 +5912,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -5929,16 +5938,16 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5988,19 +5997,19 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>18</v>
@@ -6009,7 +6018,7 @@
         <v>18</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>18</v>
@@ -6017,45 +6026,45 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6104,19 +6113,19 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>18</v>
@@ -6125,7 +6134,7 @@
         <v>18</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>18</v>
@@ -6133,10 +6142,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6144,10 +6153,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6159,16 +6168,16 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6194,11 +6203,11 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>18</v>
@@ -6216,28 +6225,28 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>18</v>
@@ -6245,10 +6254,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6256,10 +6265,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6271,16 +6280,16 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6306,13 +6315,13 @@
         <v>18</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>18</v>
@@ -6330,28 +6339,28 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>18</v>
@@ -6359,10 +6368,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6370,10 +6379,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
@@ -6385,13 +6394,13 @@
         <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6418,11 +6427,11 @@
         <v>18</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>18</v>
@@ -6440,28 +6449,28 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>18</v>
@@ -6469,10 +6478,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6480,10 +6489,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
@@ -6492,19 +6501,19 @@
         <v>18</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6554,28 +6563,28 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>18</v>
@@ -6583,10 +6592,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6594,10 +6603,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
@@ -6609,13 +6618,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6666,28 +6675,28 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>18</v>
@@ -6695,10 +6704,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6706,10 +6715,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -6721,13 +6730,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6778,13 +6787,13 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>18</v>
@@ -6799,7 +6808,7 @@
         <v>18</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>18</v>
@@ -6807,21 +6816,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -6833,16 +6842,16 @@
         <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6892,19 +6901,19 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>18</v>
@@ -6913,7 +6922,7 @@
         <v>18</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>18</v>
@@ -6921,45 +6930,45 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7008,19 +7017,19 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
@@ -7029,7 +7038,7 @@
         <v>18</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>18</v>
@@ -7037,10 +7046,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7048,10 +7057,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>18</v>
@@ -7060,16 +7069,16 @@
         <v>18</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7096,13 +7105,13 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
@@ -7120,39 +7129,39 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7160,10 +7169,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
@@ -7175,13 +7184,13 @@
         <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7232,28 +7241,28 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>18</v>
@@ -7261,21 +7270,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>18</v>
@@ -7287,13 +7296,13 @@
         <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7344,28 +7353,28 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>18</v>
@@ -7373,10 +7382,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7384,10 +7393,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>18</v>
@@ -7399,13 +7408,13 @@
         <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7456,28 +7465,28 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>18</v>
@@ -7485,10 +7494,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7496,10 +7505,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>18</v>
@@ -7508,19 +7517,19 @@
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7570,28 +7579,28 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>18</v>
@@ -7599,10 +7608,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7610,10 +7619,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>18</v>
@@ -7625,13 +7634,13 @@
         <v>18</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7682,28 +7691,28 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>18</v>
@@ -7711,10 +7720,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7722,10 +7731,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>18</v>
@@ -7737,13 +7746,13 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7794,13 +7803,13 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>18</v>
@@ -7815,7 +7824,7 @@
         <v>18</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>18</v>
@@ -7823,21 +7832,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>18</v>
@@ -7849,16 +7858,16 @@
         <v>18</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7908,19 +7917,19 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>18</v>
@@ -7929,7 +7938,7 @@
         <v>18</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>18</v>
@@ -7937,45 +7946,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8024,19 +8033,19 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>18</v>
@@ -8045,7 +8054,7 @@
         <v>18</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>18</v>
@@ -8053,10 +8062,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8064,10 +8073,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>18</v>
@@ -8076,16 +8085,16 @@
         <v>18</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8112,13 +8121,13 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
@@ -8136,39 +8145,39 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8176,10 +8185,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
@@ -8191,13 +8200,13 @@
         <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8248,28 +8257,28 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>18</v>
@@ -8277,10 +8286,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8288,10 +8297,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>18</v>
@@ -8303,13 +8312,13 @@
         <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8336,13 +8345,13 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
@@ -8360,39 +8369,39 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8400,10 +8409,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>18</v>
@@ -8415,13 +8424,13 @@
         <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8472,28 +8481,28 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>18</v>
@@ -8501,10 +8510,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8512,10 +8521,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
@@ -8527,13 +8536,13 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8584,28 +8593,28 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>18</v>
@@ -8613,10 +8622,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8624,10 +8633,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>18</v>
@@ -8639,13 +8648,13 @@
         <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8672,13 +8681,13 @@
         <v>18</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>18</v>
@@ -8696,28 +8705,28 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>18</v>
@@ -8725,10 +8734,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8736,10 +8745,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>18</v>
@@ -8751,16 +8760,16 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8810,28 +8819,28 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>18</v>
@@ -8839,10 +8848,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8850,10 +8859,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>18</v>
@@ -8865,13 +8874,13 @@
         <v>18</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8922,13 +8931,13 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>18</v>
@@ -8943,7 +8952,7 @@
         <v>18</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>18</v>
@@ -8951,21 +8960,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>18</v>
@@ -8977,16 +8986,16 @@
         <v>18</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9036,19 +9045,19 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>18</v>
@@ -9057,7 +9066,7 @@
         <v>18</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>18</v>
@@ -9065,45 +9074,45 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -9152,19 +9161,19 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>18</v>
@@ -9173,7 +9182,7 @@
         <v>18</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>18</v>
@@ -9181,21 +9190,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>18</v>
@@ -9207,13 +9216,13 @@
         <v>18</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9264,28 +9273,28 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>18</v>
@@ -9293,10 +9302,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9304,10 +9313,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>18</v>
@@ -9319,13 +9328,13 @@
         <v>18</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9376,28 +9385,28 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>18</v>
@@ -9405,10 +9414,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9416,10 +9425,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>18</v>
@@ -9431,16 +9440,16 @@
         <v>18</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9490,28 +9499,28 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>18</v>
@@ -9519,10 +9528,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9530,10 +9539,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>18</v>
@@ -9545,13 +9554,13 @@
         <v>18</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9602,28 +9611,28 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>18</v>
@@ -9631,10 +9640,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9642,10 +9651,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>18</v>
@@ -9654,19 +9663,19 @@
         <v>18</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9716,28 +9725,28 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>18</v>
@@ -9745,10 +9754,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9756,10 +9765,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>18</v>
@@ -9771,16 +9780,16 @@
         <v>18</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9830,22 +9839,22 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:35:16+00:00</t>
+    <t>2026-07-29T12:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG references but does not redistribute SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); value sets enumerate concept identifiers only, so display terms are supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
+    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG carries concept identifiers from SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); it redistributes no code system release, national extension or semantic content. Value sets enumerate identifiers, and some members additionally carry the English term as an unmodified display hint; the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:05:46+00:00</t>
+    <t>2026-07-31T09:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:21:13+00:00</t>
+    <t>2026-08-13T14:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>© 2026 N. Kapan Tunçer and S. Tunçer. IG artifacts licensed under the MIT License. This IG carries concept identifiers from SNOMED CT (© SNOMED International), LOINC (© Regenstrief Institute, Inc.) and the IDDSI framework (CC BY-SA 4.0, used unmodified); it redistributes no code system release, national extension or semantic content. Value sets enumerate identifiers, and some members additionally carry the English term as an unmodified display hint; the authoritative display is supplied at expansion time by the implementer's own terminology server. Implementers are responsible for holding the applicable third-party licences.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. The IDDSI framework is used unmodified under CC BY-SA 4.0; no IDDSI document text, table, image or testing method is reproduced. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:50+00:00</t>
+    <t>2026-08-13T23:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0) and reproduced verbatim, with none translated, shortened or otherwise altered. The IDDSI framework is used unmodified under CC BY-SA 4.0; no IDDSI document text, table, image or testing method is reproduced. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
+    <t>Profile definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). This profile carries third-party concept identifiers rather than the terminologies themselves. SNOMED CT® is a registered trademark of SNOMED International; concept identifiers and English terms are © SNOMED International, used under the Global Patient Set licence (CC BY-ND 4.0, https://creativecommons.org/licenses/by-nd/4.0/) and reproduced verbatim, with none translated, shortened or otherwise altered. The IDDSI framework is used unmodified under CC BY-SA 4.0; no IDDSI document text, table, image or testing method is reproduced. Implementers remain responsible for holding the applicable third-party licences in their own territory.</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.2</t>
+    <t>1.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:31:20+00:00</t>
+    <t>2026-08-14T00:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.3</t>
+    <t>1.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:08:39+00:00</t>
+    <t>2026-08-14T00:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.4</t>
+    <t>1.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:48:45+00:00</t>
+    <t>2026-08-15T14:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.5</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T14:40:00+00:00</t>
+    <t>2026-08-18T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T10:55:39+00:00</t>
+    <t>2026-08-18T13:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:05:08+00:00</t>
+    <t>2026-08-18T14:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dysphagia-nutrition-order.xlsx
+++ b/StructureDefinition-dysphagia-nutrition-order.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:23:53+00:00</t>
+    <t>2026-08-19T10:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
